--- a/Salida.xlsx
+++ b/Salida.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Salida.xlsx
+++ b/Salida.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,16 +485,16 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -517,16 +517,16 @@
         <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,16 +549,16 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -613,16 +613,16 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -645,16 +645,16 @@
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -677,16 +677,16 @@
         <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>-13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -709,16 +709,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>474</v>
+        <v>210</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>474</v>
+        <v>210</v>
       </c>
       <c r="G9" t="n">
-        <v>-474</v>
+        <v>-210</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -741,16 +741,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="F10" t="n">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="G10" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
@@ -837,16 +837,16 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>39</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43</v>
+      </c>
+      <c r="G13" t="n">
         <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -869,16 +869,16 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -901,16 +901,16 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -933,16 +933,16 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -965,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F17" t="n">
-        <v>242</v>
+        <v>279</v>
       </c>
       <c r="G17" t="n">
-        <v>-42</v>
+        <v>-29</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -997,16 +997,16 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>-10</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1061,16 +1061,16 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1096,10 +1096,10 @@
         <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1125,16 +1125,16 @@
         <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="G22" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1157,16 +1157,16 @@
         <v>3</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1189,16 +1189,16 @@
         <v>14</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E24" t="n">
-        <v>102</v>
+        <v>150</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="G24" t="n">
-        <v>-9</v>
+        <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1221,16 +1221,16 @@
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F25" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1253,16 +1253,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F26" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G26" t="n">
-        <v>-19</v>
+        <v>-6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1285,16 +1285,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F27" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="G27" t="n">
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1317,16 +1317,16 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E28" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F28" t="n">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="G28" t="n">
-        <v>-16</v>
+        <v>-7</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1349,16 +1349,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="F29" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="G29" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F30" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="G30" t="n">
-        <v>-21</v>
+        <v>-4</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F31" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="G31" t="n">
-        <v>-16</v>
+        <v>-11</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1445,16 +1445,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="G32" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -1477,16 +1477,16 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G33" t="n">
-        <v>-20</v>
+        <v>-11</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -1509,16 +1509,16 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E34" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F34" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G34" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -1541,16 +1541,16 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="F35" t="n">
-        <v>53</v>
+        <v>214</v>
       </c>
       <c r="G35" t="n">
-        <v>-23</v>
+        <v>-4</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -1573,16 +1573,16 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F36" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="G36" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -1637,16 +1637,16 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F38" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="G38" t="n">
-        <v>-18</v>
+        <v>-15</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -1669,16 +1669,16 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="F39" t="n">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="G39" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -1701,16 +1701,16 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F40" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G40" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -1733,16 +1733,16 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F41" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="G41" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -1765,16 +1765,16 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F42" t="n">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="G42" t="n">
-        <v>-19</v>
+        <v>-6</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -1797,16 +1797,16 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F43" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="G43" t="n">
-        <v>-18</v>
+        <v>-13</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -1829,16 +1829,16 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F44" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G44" t="n">
-        <v>-19</v>
+        <v>-2</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -1861,16 +1861,16 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F45" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="G45" t="n">
-        <v>-29</v>
+        <v>-9</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -1893,16 +1893,16 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
+        <v>12</v>
+      </c>
+      <c r="E46" t="n">
         <v>10</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
       <c r="F46" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G46" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -1957,16 +1957,16 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E48" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F48" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="G48" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -1989,16 +1989,16 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="F49" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="G49" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -2021,16 +2021,16 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -2053,16 +2053,16 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -2085,16 +2085,16 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E52" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F52" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="G52" t="n">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F55" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="G55" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -2213,16 +2213,16 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F56" t="n">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="G56" t="n">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -2245,16 +2245,16 @@
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E57" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F57" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="G57" t="n">
-        <v>-17</v>
+        <v>-13</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2277,16 +2277,16 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E58" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G58" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         <v>16</v>
       </c>
       <c r="E59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G59" t="n">
         <v>-16</v>
@@ -2341,16 +2341,16 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F60" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="G60" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -2373,16 +2373,16 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E61" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F61" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="G61" t="n">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -2405,16 +2405,16 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F62" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G62" t="n">
-        <v>-11</v>
+        <v>-2</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -2437,16 +2437,16 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E63" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F63" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G63" t="n">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -2469,16 +2469,16 @@
         <v>20</v>
       </c>
       <c r="D64" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="G64" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Croissant Alargado Fresco Jamon Queso</t>
+          <t>Croissant Alargado Jamon Queso Fresco</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2629,16 +2629,16 @@
         <v>30</v>
       </c>
       <c r="D69" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G69" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -2661,16 +2661,16 @@
         <v>15</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G70" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -2693,16 +2693,16 @@
         <v>15</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -2757,16 +2757,16 @@
         <v>15</v>
       </c>
       <c r="D73" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -2792,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G74" t="n">
         <v>15</v>
@@ -2821,16 +2821,16 @@
         <v>15</v>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -2885,16 +2885,16 @@
         <v>15</v>
       </c>
       <c r="D77" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F77" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -2917,16 +2917,16 @@
         <v>15</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G78" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -2981,16 +2981,16 @@
         <v>15</v>
       </c>
       <c r="D80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -3013,16 +3013,16 @@
         <v>10</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -3048,10 +3048,10 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G82" t="n">
         <v>10</v>
@@ -3077,16 +3077,16 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E83" t="n">
-        <v>240</v>
+        <v>760</v>
       </c>
       <c r="F83" t="n">
-        <v>270</v>
+        <v>805</v>
       </c>
       <c r="G83" t="n">
-        <v>-30</v>
+        <v>-45</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -3109,16 +3109,16 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>51</v>
+        <v>-3</v>
       </c>
       <c r="E84" t="n">
-        <v>240</v>
+        <v>930</v>
       </c>
       <c r="F84" t="n">
-        <v>291</v>
+        <v>927</v>
       </c>
       <c r="G84" t="n">
-        <v>-51</v>
+        <v>3</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -3141,16 +3141,16 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="E85" t="n">
-        <v>400</v>
+        <v>1050</v>
       </c>
       <c r="F85" t="n">
-        <v>422</v>
+        <v>1125</v>
       </c>
       <c r="G85" t="n">
-        <v>-22</v>
+        <v>-75</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -3173,16 +3173,16 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>949</v>
+        <v>997</v>
       </c>
       <c r="E86" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1949</v>
+        <v>997</v>
       </c>
       <c r="G86" t="n">
-        <v>-949</v>
+        <v>-997</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -3205,16 +3205,16 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>-469</v>
+        <v>-530</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>-469</v>
+        <v>-530</v>
       </c>
       <c r="G87" t="n">
-        <v>469</v>
+        <v>530</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ins. Bolsa Palta Hass Salsa HD</t>
+          <t>ELIMINAR Ins. Bolsa Palta Hass Salsa HD</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3240,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>21.785</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -3272,10 +3272,10 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F89" t="n">
-        <v>4.855</v>
+        <v>12.455</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -3304,10 +3304,10 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F90" t="n">
-        <v>3.82</v>
+        <v>10.455</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -3365,16 +3365,16 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F92" t="n">
-        <v>11.949</v>
+        <v>9.786</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -3397,16 +3397,16 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F93" t="n">
-        <v>6.9</v>
+        <v>16.455</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -3429,16 +3429,16 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F94" t="n">
-        <v>13.161</v>
+        <v>33.992</v>
       </c>
       <c r="G94" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -3461,16 +3461,16 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F95" t="n">
-        <v>14.426</v>
+        <v>20.559</v>
       </c>
       <c r="G95" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -3493,16 +3493,16 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E96" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F96" t="n">
-        <v>10.288</v>
+        <v>22.804</v>
       </c>
       <c r="G96" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -3525,16 +3525,16 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E97" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F97" t="n">
-        <v>9.645</v>
+        <v>5.176</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -3557,16 +3557,16 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E98" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F98" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G98" t="n">
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -3589,16 +3589,16 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="F99" t="n">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="G99" t="n">
-        <v>-14</v>
+        <v>-5</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -3621,16 +3621,16 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>90</v>
+        <v>620</v>
       </c>
       <c r="E100" t="n">
-        <v>1500</v>
+        <v>2470</v>
       </c>
       <c r="F100" t="n">
-        <v>1590</v>
+        <v>3090</v>
       </c>
       <c r="G100" t="n">
-        <v>-90</v>
+        <v>-620</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -3653,16 +3653,16 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F101" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G101" t="n">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -3685,16 +3685,16 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>950</v>
+        <v>-573</v>
       </c>
       <c r="E102" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="F102" t="n">
-        <v>1950</v>
+        <v>2427</v>
       </c>
       <c r="G102" t="n">
-        <v>-950</v>
+        <v>573</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -3717,16 +3717,16 @@
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>949</v>
+        <v>347</v>
       </c>
       <c r="E103" t="n">
         <v>1000</v>
       </c>
       <c r="F103" t="n">
-        <v>1949</v>
+        <v>1347</v>
       </c>
       <c r="G103" t="n">
-        <v>-949</v>
+        <v>-347</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -3749,16 +3749,16 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>-469</v>
+        <v>-530</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>-469</v>
+        <v>-530</v>
       </c>
       <c r="G104" t="n">
-        <v>469</v>
+        <v>530</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -3781,16 +3781,16 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>-650</v>
+        <v>0</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -3813,16 +3813,16 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>-50</v>
+        <v>404</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>-50</v>
+        <v>404</v>
       </c>
       <c r="G106" t="n">
-        <v>50</v>
+        <v>-404</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -3845,16 +3845,16 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>-79</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -3877,16 +3877,16 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>402</v>
+        <v>246</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F108" t="n">
-        <v>402</v>
+        <v>746</v>
       </c>
       <c r="G108" t="n">
-        <v>-402</v>
+        <v>-246</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -3909,16 +3909,16 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
+        <v>-123</v>
+      </c>
+      <c r="E109" t="n">
         <v>275</v>
       </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
       <c r="F109" t="n">
-        <v>275</v>
+        <v>152</v>
       </c>
       <c r="G109" t="n">
-        <v>-275</v>
+        <v>123</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -3941,16 +3941,16 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E110" t="n">
-        <v>350</v>
+        <v>625</v>
       </c>
       <c r="F110" t="n">
-        <v>378</v>
+        <v>666</v>
       </c>
       <c r="G110" t="n">
-        <v>-28</v>
+        <v>-41</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -3973,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>800</v>
+        <v>120</v>
       </c>
       <c r="G111" t="n">
-        <v>-800</v>
+        <v>-120</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -4037,16 +4037,16 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>430</v>
+        <v>1207</v>
       </c>
       <c r="E113" t="n">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F113" t="n">
-        <v>3430</v>
+        <v>5207</v>
       </c>
       <c r="G113" t="n">
-        <v>-430</v>
+        <v>-1207</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -4069,16 +4069,16 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E114" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="F114" t="n">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="G114" t="n">
-        <v>-23</v>
+        <v>-27</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -4101,16 +4101,16 @@
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>23</v>
+        <v>-2</v>
       </c>
       <c r="E115" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F115" t="n">
-        <v>40</v>
+        <v>-2</v>
       </c>
       <c r="G115" t="n">
-        <v>-23</v>
+        <v>2</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -4133,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G117" t="n">
         <v>5</v>
@@ -4200,10 +4200,10 @@
         <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F118" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G118" t="n">
         <v>-7</v>
@@ -4229,16 +4229,16 @@
         <v>5</v>
       </c>
       <c r="D119" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E119" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G119" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -4261,16 +4261,16 @@
         <v>5</v>
       </c>
       <c r="D120" t="n">
+        <v>5</v>
+      </c>
+      <c r="E120" t="n">
         <v>6</v>
       </c>
-      <c r="E120" t="n">
-        <v>12</v>
-      </c>
       <c r="F120" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G120" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -4293,16 +4293,16 @@
         <v>6</v>
       </c>
       <c r="D121" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E121" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         <v>17</v>
       </c>
       <c r="E122" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F122" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G122" t="n">
         <v>-11</v>
@@ -4357,16 +4357,16 @@
         <v>6</v>
       </c>
       <c r="D123" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E123" t="n">
         <v>12</v>
       </c>
       <c r="F123" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G123" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -4389,16 +4389,16 @@
         <v>6</v>
       </c>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F124" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>6</v>
       </c>
       <c r="D125" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E125" t="n">
         <v>12</v>
       </c>
       <c r="F125" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G125" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -4453,16 +4453,16 @@
         <v>6</v>
       </c>
       <c r="D126" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E126" t="n">
         <v>12</v>
       </c>
       <c r="F126" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G126" t="n">
-        <v>-11</v>
+        <v>-15</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -4485,16 +4485,16 @@
         <v>6</v>
       </c>
       <c r="D127" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E127" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F127" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G127" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -4549,16 +4549,16 @@
         <v>7</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G129" t="n">
-        <v>7</v>
+        <v>-6</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -4581,16 +4581,16 @@
         <v>10</v>
       </c>
       <c r="D130" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E130" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F130" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="G130" t="n">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -4613,16 +4613,16 @@
         <v>12</v>
       </c>
       <c r="D131" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E131" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F131" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G131" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -4645,16 +4645,16 @@
         <v>10</v>
       </c>
       <c r="D132" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E132" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F132" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="G132" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -4677,16 +4677,16 @@
         <v>18</v>
       </c>
       <c r="D133" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E133" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F133" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G133" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -4709,16 +4709,16 @@
         <v>6</v>
       </c>
       <c r="D134" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E134" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F134" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G134" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -4741,16 +4741,16 @@
         <v>7</v>
       </c>
       <c r="D135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E135" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F135" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G135" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -4773,16 +4773,16 @@
         <v>7</v>
       </c>
       <c r="D136" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E136" t="n">
         <v>4</v>
       </c>
       <c r="F136" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G136" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -4805,16 +4805,16 @@
         <v>5</v>
       </c>
       <c r="D137" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E137" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F137" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G137" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -4837,16 +4837,16 @@
         <v>6</v>
       </c>
       <c r="D138" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E138" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F138" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G138" t="n">
-        <v>-16</v>
+        <v>-8</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -4872,10 +4872,10 @@
         <v>20</v>
       </c>
       <c r="E139" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="G139" t="n">
         <v>-5</v>
@@ -4901,16 +4901,16 @@
         <v>18</v>
       </c>
       <c r="D140" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E140" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="F140" t="n">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="G140" t="n">
-        <v>-24</v>
+        <v>-11</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -4965,16 +4965,16 @@
         <v>5</v>
       </c>
       <c r="D142" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E142" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F142" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G142" t="n">
-        <v>-17</v>
+        <v>-22</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -4997,16 +4997,16 @@
         <v>18</v>
       </c>
       <c r="D143" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="E143" t="n">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="F143" t="n">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="G143" t="n">
-        <v>-15</v>
+        <v>11</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -5029,16 +5029,16 @@
         <v>22</v>
       </c>
       <c r="D144" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="E144" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F144" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G144" t="n">
-        <v>-25</v>
+        <v>-2</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -5061,16 +5061,16 @@
         <v>6</v>
       </c>
       <c r="D145" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="G145" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -5093,16 +5093,16 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F146" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G146" t="n">
-        <v>-31</v>
+        <v>-11</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -5125,16 +5125,16 @@
         <v>5</v>
       </c>
       <c r="D147" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E147" t="n">
         <v>6</v>
       </c>
       <c r="F147" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -5157,16 +5157,16 @@
         <v>22</v>
       </c>
       <c r="D148" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F148" t="n">
         <v>31</v>
       </c>
       <c r="G148" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -5189,16 +5189,16 @@
         <v>5</v>
       </c>
       <c r="D149" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E149" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F149" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G149" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -5221,16 +5221,16 @@
         <v>6</v>
       </c>
       <c r="D150" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F150" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="G150" t="n">
-        <v>-3</v>
+        <v>-15</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -5253,16 +5253,16 @@
         <v>14</v>
       </c>
       <c r="D151" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E151" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="F151" t="n">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="G151" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -5285,16 +5285,16 @@
         <v>6</v>
       </c>
       <c r="D152" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="E152" t="n">
         <v>24</v>
       </c>
       <c r="F152" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G152" t="n">
-        <v>-3</v>
+        <v>10</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -5317,16 +5317,16 @@
         <v>5</v>
       </c>
       <c r="D153" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E153" t="n">
         <v>6</v>
       </c>
       <c r="F153" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G153" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -5349,16 +5349,16 @@
         <v>6</v>
       </c>
       <c r="D154" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F154" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="G154" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -5381,16 +5381,16 @@
         <v>5</v>
       </c>
       <c r="D155" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F155" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G155" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -5413,16 +5413,16 @@
         <v>6</v>
       </c>
       <c r="D156" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F156" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -5445,16 +5445,16 @@
         <v>28</v>
       </c>
       <c r="D157" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E157" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F157" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G157" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -5512,10 +5512,10 @@
         <v>17</v>
       </c>
       <c r="E159" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F159" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G159" t="n">
         <v>-11</v>
@@ -5541,16 +5541,16 @@
         <v>5</v>
       </c>
       <c r="D160" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E160" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F160" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G160" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -5573,16 +5573,16 @@
         <v>6</v>
       </c>
       <c r="D161" t="n">
+        <v>9</v>
+      </c>
+      <c r="E161" t="n">
         <v>12</v>
       </c>
-      <c r="E161" t="n">
-        <v>6</v>
-      </c>
       <c r="F161" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G161" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -5605,16 +5605,16 @@
         <v>5</v>
       </c>
       <c r="D162" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E162" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F162" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G162" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -5637,16 +5637,16 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5669,16 +5669,16 @@
         <v>42</v>
       </c>
       <c r="D164" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F164" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="G164" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -5701,16 +5701,16 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E165" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="F165" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="G165" t="n">
-        <v>-6</v>
+        <v>-13</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -5733,16 +5733,16 @@
         <v>5</v>
       </c>
       <c r="D166" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E166" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F166" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G166" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -5765,16 +5765,16 @@
         <v>6</v>
       </c>
       <c r="D167" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E167" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F167" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G167" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -5800,10 +5800,10 @@
         <v>10</v>
       </c>
       <c r="E168" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F168" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G168" t="n">
         <v>-5</v>
@@ -5829,16 +5829,16 @@
         <v>6</v>
       </c>
       <c r="D169" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E169" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="F169" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="G169" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5861,16 +5861,16 @@
         <v>3</v>
       </c>
       <c r="D170" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
         <v>12</v>
       </c>
       <c r="F170" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G170" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5893,16 +5893,16 @@
         <v>5</v>
       </c>
       <c r="D171" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E171" t="n">
         <v>12</v>
       </c>
       <c r="F171" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G171" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -5957,16 +5957,16 @@
         <v>7</v>
       </c>
       <c r="D173" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F173" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G173" t="n">
-        <v>-9</v>
+        <v>6</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -5989,16 +5989,16 @@
         <v>30</v>
       </c>
       <c r="D174" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="G174" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -6021,16 +6021,16 @@
         <v>30</v>
       </c>
       <c r="D175" t="n">
+        <v>5</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="n">
+        <v>5</v>
+      </c>
+      <c r="G175" t="n">
         <v>25</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0</v>
-      </c>
-      <c r="F175" t="n">
-        <v>25</v>
-      </c>
-      <c r="G175" t="n">
-        <v>5</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -6053,16 +6053,16 @@
         <v>15</v>
       </c>
       <c r="D176" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -6085,16 +6085,16 @@
         <v>15</v>
       </c>
       <c r="D177" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G177" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>30</v>
       </c>
       <c r="D178" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G178" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -6149,16 +6149,16 @@
         <v>15</v>
       </c>
       <c r="D179" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
       </c>
       <c r="F179" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G179" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -6181,16 +6181,16 @@
         <v>30</v>
       </c>
       <c r="D180" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -6213,16 +6213,16 @@
         <v>32</v>
       </c>
       <c r="D181" t="n">
+        <v>18</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>18</v>
+      </c>
+      <c r="G181" t="n">
         <v>14</v>
-      </c>
-      <c r="E181" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" t="n">
-        <v>14</v>
-      </c>
-      <c r="G181" t="n">
-        <v>18</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -6309,16 +6309,16 @@
         <v>32</v>
       </c>
       <c r="D184" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G184" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -6341,16 +6341,16 @@
         <v>32</v>
       </c>
       <c r="D185" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G185" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -6373,16 +6373,16 @@
         <v>30</v>
       </c>
       <c r="D186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -6405,16 +6405,16 @@
         <v>30</v>
       </c>
       <c r="D187" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G187" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -6437,16 +6437,16 @@
         <v>28</v>
       </c>
       <c r="D188" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -6469,16 +6469,16 @@
         <v>28</v>
       </c>
       <c r="D189" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G189" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -6533,16 +6533,16 @@
         <v>28</v>
       </c>
       <c r="D191" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G191" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -6597,16 +6597,16 @@
         <v>28</v>
       </c>
       <c r="D193" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G193" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -6661,16 +6661,16 @@
         <v>28</v>
       </c>
       <c r="D195" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G195" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -6725,16 +6725,16 @@
         <v>40</v>
       </c>
       <c r="D197" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G197" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -6757,16 +6757,16 @@
         <v>40</v>
       </c>
       <c r="D198" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G198" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -6789,16 +6789,16 @@
         <v>32</v>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -6949,16 +6949,16 @@
         <v>35</v>
       </c>
       <c r="D204" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G204" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -6981,16 +6981,16 @@
         <v>30</v>
       </c>
       <c r="D205" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G205" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -7013,16 +7013,16 @@
         <v>45</v>
       </c>
       <c r="D206" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
       </c>
       <c r="F206" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G206" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -7048,10 +7048,10 @@
         <v>10</v>
       </c>
       <c r="E207" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F207" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="G207" t="n">
         <v>-3</v>
@@ -7077,16 +7077,16 @@
         <v>14</v>
       </c>
       <c r="D208" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E208" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F208" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -7109,16 +7109,16 @@
         <v>14</v>
       </c>
       <c r="D209" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E209" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F209" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G209" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -7141,16 +7141,16 @@
         <v>7</v>
       </c>
       <c r="D210" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E210" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F210" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G210" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -7173,16 +7173,16 @@
         <v>7</v>
       </c>
       <c r="D211" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E211" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F211" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G211" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -7205,16 +7205,16 @@
         <v>7</v>
       </c>
       <c r="D212" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E212" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F212" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="G212" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -7237,16 +7237,16 @@
         <v>7</v>
       </c>
       <c r="D213" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="E213" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F213" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G213" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -7301,16 +7301,16 @@
         <v>22</v>
       </c>
       <c r="D215" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="E215" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="F215" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G215" t="n">
-        <v>-33</v>
+        <v>-5</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -7333,16 +7333,16 @@
         <v>14</v>
       </c>
       <c r="D216" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
       </c>
       <c r="F216" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G216" t="n">
-        <v>-14</v>
+        <v>-5</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -7365,16 +7365,16 @@
         <v>14</v>
       </c>
       <c r="D217" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E217" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F217" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="G217" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -7397,16 +7397,16 @@
         <v>14</v>
       </c>
       <c r="D218" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E218" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F218" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G218" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -7429,16 +7429,16 @@
         <v>14</v>
       </c>
       <c r="D219" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E219" t="n">
         <v>30</v>
       </c>
       <c r="F219" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G219" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -7461,16 +7461,16 @@
         <v>14</v>
       </c>
       <c r="D220" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F220" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="G220" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -7493,16 +7493,16 @@
         <v>14</v>
       </c>
       <c r="D221" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E221" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F221" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="G221" t="n">
-        <v>10</v>
+        <v>-3</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -7525,16 +7525,16 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E222" t="n">
         <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -7557,16 +7557,16 @@
         <v>14</v>
       </c>
       <c r="D223" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E223" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F223" t="n">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="G223" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -7589,16 +7589,16 @@
         <v>7</v>
       </c>
       <c r="D224" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E224" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>-11</v>
+        <v>7</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -7621,16 +7621,16 @@
         <v>5</v>
       </c>
       <c r="D225" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E225" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F225" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G225" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -7653,16 +7653,16 @@
         <v>5</v>
       </c>
       <c r="D226" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E226" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F226" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G226" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -7685,16 +7685,16 @@
         <v>5</v>
       </c>
       <c r="D227" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F227" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G227" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -7749,16 +7749,16 @@
         <v>10</v>
       </c>
       <c r="D229" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E229" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F229" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G229" t="n">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -7781,16 +7781,16 @@
         <v>5</v>
       </c>
       <c r="D230" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E230" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F230" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G230" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>15</v>
       </c>
       <c r="D231" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E231" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F231" t="n">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="G231" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -7845,16 +7845,16 @@
         <v>15</v>
       </c>
       <c r="D232" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E232" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F232" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G232" t="n">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -7877,16 +7877,16 @@
         <v>15</v>
       </c>
       <c r="D233" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G233" t="n">
-        <v>-12</v>
+        <v>9</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -7912,10 +7912,10 @@
         <v>12</v>
       </c>
       <c r="E234" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="F234" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="G234" t="n">
         <v>3</v>
@@ -7941,16 +7941,16 @@
         <v>15</v>
       </c>
       <c r="D235" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E235" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="F235" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="G235" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -7973,16 +7973,16 @@
         <v>30</v>
       </c>
       <c r="D236" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="E236" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F236" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G236" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -8005,16 +8005,16 @@
         <v>30</v>
       </c>
       <c r="D237" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E237" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F237" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G237" t="n">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         <v>15</v>
       </c>
       <c r="E238" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F238" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G238" t="n">
         <v>-7</v>
@@ -8069,16 +8069,16 @@
         <v>30</v>
       </c>
       <c r="D239" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E239" t="n">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="F239" t="n">
-        <v>33</v>
+        <v>199</v>
       </c>
       <c r="G239" t="n">
-        <v>21</v>
+        <v>-1</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -8101,16 +8101,16 @@
         <v>30</v>
       </c>
       <c r="D240" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F240" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="G240" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -8133,16 +8133,16 @@
         <v>12</v>
       </c>
       <c r="D241" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E241" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="F241" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="G241" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -8197,16 +8197,16 @@
         <v>15</v>
       </c>
       <c r="D243" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E243" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F243" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="G243" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -8229,16 +8229,16 @@
         <v>15</v>
       </c>
       <c r="D244" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E244" t="n">
         <v>0</v>
       </c>
       <c r="F244" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>-4</v>
+        <v>15</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -8261,16 +8261,16 @@
         <v>6</v>
       </c>
       <c r="D245" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E245" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G245" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -8293,16 +8293,16 @@
         <v>5</v>
       </c>
       <c r="D246" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E246" t="n">
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G246" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -8325,16 +8325,16 @@
         <v>6</v>
       </c>
       <c r="D247" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E247" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="G247" t="n">
-        <v>-24</v>
+        <v>-11</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -8357,16 +8357,16 @@
         <v>20</v>
       </c>
       <c r="D248" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E248" t="n">
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G248" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -8389,16 +8389,16 @@
         <v>10</v>
       </c>
       <c r="D249" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E249" t="n">
         <v>12</v>
       </c>
       <c r="F249" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G249" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -8421,16 +8421,16 @@
         <v>32</v>
       </c>
       <c r="D250" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E250" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="F250" t="n">
-        <v>203</v>
+        <v>70</v>
       </c>
       <c r="G250" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -8488,10 +8488,10 @@
         <v>35</v>
       </c>
       <c r="E252" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="F252" t="n">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="G252" t="n">
         <v>5</v>
@@ -8517,16 +8517,16 @@
         <v>40</v>
       </c>
       <c r="D253" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E253" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="F253" t="n">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="G253" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -8549,16 +8549,16 @@
         <v>40</v>
       </c>
       <c r="D254" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E254" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F254" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="G254" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -8581,16 +8581,16 @@
         <v>25</v>
       </c>
       <c r="D255" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E255" t="n">
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>-19</v>
+        <v>25</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -8613,16 +8613,16 @@
         <v>25</v>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E256" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="G256" t="n">
-        <v>24</v>
+        <v>-21</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -8645,16 +8645,16 @@
         <v>8</v>
       </c>
       <c r="D257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E257" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F257" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G257" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -8677,16 +8677,16 @@
         <v>8</v>
       </c>
       <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
         <v>8</v>
-      </c>
-      <c r="E258" t="n">
-        <v>0</v>
-      </c>
-      <c r="F258" t="n">
-        <v>8</v>
-      </c>
-      <c r="G258" t="n">
-        <v>0</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -8709,16 +8709,16 @@
         <v>8</v>
       </c>
       <c r="D259" t="n">
+        <v>2</v>
+      </c>
+      <c r="E259" t="n">
+        <v>8</v>
+      </c>
+      <c r="F259" t="n">
+        <v>10</v>
+      </c>
+      <c r="G259" t="n">
         <v>6</v>
-      </c>
-      <c r="E259" t="n">
-        <v>0</v>
-      </c>
-      <c r="F259" t="n">
-        <v>6</v>
-      </c>
-      <c r="G259" t="n">
-        <v>2</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -8741,16 +8741,16 @@
         <v>8</v>
       </c>
       <c r="D260" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E260" t="n">
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -8773,16 +8773,16 @@
         <v>8</v>
       </c>
       <c r="D261" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E261" t="n">
         <v>0</v>
       </c>
       <c r="F261" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -8805,16 +8805,16 @@
         <v>8</v>
       </c>
       <c r="D262" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -8837,16 +8837,16 @@
         <v>8</v>
       </c>
       <c r="D263" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F263" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G263" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -8869,16 +8869,16 @@
         <v>8</v>
       </c>
       <c r="D264" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F264" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G264" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -8901,16 +8901,16 @@
         <v>8</v>
       </c>
       <c r="D265" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E265" t="n">
         <v>0</v>
       </c>
       <c r="F265" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -8933,16 +8933,16 @@
         <v>8</v>
       </c>
       <c r="D266" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E266" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F266" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G266" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -9029,16 +9029,16 @@
         <v>8</v>
       </c>
       <c r="D269" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E269" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F269" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G269" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -9093,16 +9093,16 @@
         <v>8</v>
       </c>
       <c r="D271" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F271" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G271" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -9125,16 +9125,16 @@
         <v>8</v>
       </c>
       <c r="D272" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F272" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G272" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -9253,16 +9253,16 @@
         <v>8</v>
       </c>
       <c r="D276" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G276" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -9285,16 +9285,16 @@
         <v>20</v>
       </c>
       <c r="D277" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F277" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="G277" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -9317,16 +9317,16 @@
         <v>20</v>
       </c>
       <c r="D278" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E278" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F278" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G278" t="n">
-        <v>-9</v>
+        <v>3</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -9349,16 +9349,16 @@
         <v>28</v>
       </c>
       <c r="D279" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E279" t="n">
+        <v>11</v>
+      </c>
+      <c r="F279" t="n">
         <v>49</v>
       </c>
-      <c r="F279" t="n">
-        <v>90</v>
-      </c>
       <c r="G279" t="n">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -9381,16 +9381,16 @@
         <v>28</v>
       </c>
       <c r="D280" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="E280" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="G280" t="n">
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -9413,16 +9413,16 @@
         <v>40</v>
       </c>
       <c r="D281" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F281" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G281" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -9477,16 +9477,16 @@
         <v>35</v>
       </c>
       <c r="D283" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E283" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F283" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="G283" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -9509,16 +9509,16 @@
         <v>32</v>
       </c>
       <c r="D284" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E284" t="n">
         <v>0</v>
       </c>
       <c r="F284" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G284" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -9541,16 +9541,16 @@
         <v>15</v>
       </c>
       <c r="D285" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E285" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F285" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G285" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -9573,16 +9573,16 @@
         <v>15</v>
       </c>
       <c r="D286" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E286" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F286" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G286" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -9605,16 +9605,16 @@
         <v>15</v>
       </c>
       <c r="D287" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E287" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F287" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G287" t="n">
-        <v>-9</v>
+        <v>2</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -9640,10 +9640,10 @@
         <v>7</v>
       </c>
       <c r="E288" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F288" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G288" t="n">
         <v>-1</v>
@@ -9689,7 +9689,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Barra Wild Protein Vegana Chocolate 45g</t>
+          <t>Barra Wild Protein Vegana Choc Bitter45g</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9701,16 +9701,16 @@
         <v>9</v>
       </c>
       <c r="D290" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E290" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="F290" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G290" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -9765,16 +9765,16 @@
         <v>21</v>
       </c>
       <c r="D292" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E292" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F292" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G292" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -9797,16 +9797,16 @@
         <v>60</v>
       </c>
       <c r="D293" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E293" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F293" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="G293" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -9829,16 +9829,16 @@
         <v>36</v>
       </c>
       <c r="D294" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F294" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="G294" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -9893,16 +9893,16 @@
         <v>36</v>
       </c>
       <c r="D296" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E296" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F296" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G296" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -9928,10 +9928,10 @@
         <v>28</v>
       </c>
       <c r="E297" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F297" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G297" t="n">
         <v>8</v>
@@ -9957,16 +9957,16 @@
         <v>35</v>
       </c>
       <c r="D298" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E298" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="F298" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="G298" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -9989,16 +9989,16 @@
         <v>36</v>
       </c>
       <c r="D299" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E299" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F299" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="G299" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -10021,16 +10021,16 @@
         <v>36</v>
       </c>
       <c r="D300" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E300" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F300" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="G300" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -10053,16 +10053,16 @@
         <v>36</v>
       </c>
       <c r="D301" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E301" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F301" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="G301" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -10085,16 +10085,16 @@
         <v>36</v>
       </c>
       <c r="D302" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E302" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F302" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="G302" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -10149,16 +10149,16 @@
         <v>36</v>
       </c>
       <c r="D304" t="n">
+        <v>11</v>
+      </c>
+      <c r="E304" t="n">
+        <v>18</v>
+      </c>
+      <c r="F304" t="n">
         <v>29</v>
       </c>
-      <c r="E304" t="n">
-        <v>36</v>
-      </c>
-      <c r="F304" t="n">
-        <v>65</v>
-      </c>
       <c r="G304" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -10181,16 +10181,16 @@
         <v>35</v>
       </c>
       <c r="D305" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E305" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F305" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="G305" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -10213,16 +10213,16 @@
         <v>15</v>
       </c>
       <c r="D306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E306" t="n">
         <v>0</v>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -10245,16 +10245,16 @@
         <v>20</v>
       </c>
       <c r="D307" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E307" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F307" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="G307" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -10277,16 +10277,16 @@
         <v>20</v>
       </c>
       <c r="D308" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E308" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F308" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -10309,16 +10309,16 @@
         <v>15</v>
       </c>
       <c r="D309" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E309" t="n">
         <v>0</v>
       </c>
       <c r="F309" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G309" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -10341,16 +10341,16 @@
         <v>30</v>
       </c>
       <c r="D310" t="n">
+        <v>6</v>
+      </c>
+      <c r="E310" t="n">
+        <v>12</v>
+      </c>
+      <c r="F310" t="n">
         <v>18</v>
       </c>
-      <c r="E310" t="n">
-        <v>39</v>
-      </c>
-      <c r="F310" t="n">
-        <v>57</v>
-      </c>
       <c r="G310" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -10373,16 +10373,16 @@
         <v>30</v>
       </c>
       <c r="D311" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E311" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="F311" t="n">
+        <v>42</v>
+      </c>
+      <c r="G311" t="n">
         <v>21</v>
-      </c>
-      <c r="G311" t="n">
-        <v>20</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -10405,16 +10405,16 @@
         <v>18</v>
       </c>
       <c r="D312" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E312" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F312" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="G312" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -10437,16 +10437,16 @@
         <v>12</v>
       </c>
       <c r="D313" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E313" t="n">
         <v>0</v>
       </c>
       <c r="F313" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -10501,16 +10501,16 @@
         <v>50</v>
       </c>
       <c r="D315" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="E315" t="n">
         <v>20</v>
       </c>
       <c r="F315" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G315" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -10533,16 +10533,16 @@
         <v>25</v>
       </c>
       <c r="D316" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="E316" t="n">
         <v>0</v>
       </c>
       <c r="F316" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G316" t="n">
-        <v>-5</v>
+        <v>-26</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -10565,16 +10565,16 @@
         <v>25</v>
       </c>
       <c r="D317" t="n">
+        <v>4</v>
+      </c>
+      <c r="E317" t="n">
+        <v>0</v>
+      </c>
+      <c r="F317" t="n">
+        <v>4</v>
+      </c>
+      <c r="G317" t="n">
         <v>21</v>
-      </c>
-      <c r="E317" t="n">
-        <v>60</v>
-      </c>
-      <c r="F317" t="n">
-        <v>81</v>
-      </c>
-      <c r="G317" t="n">
-        <v>4</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -10597,16 +10597,16 @@
         <v>25</v>
       </c>
       <c r="D318" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E318" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F318" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="G318" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -10629,16 +10629,16 @@
         <v>50</v>
       </c>
       <c r="D319" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E319" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F319" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="G319" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -10661,16 +10661,16 @@
         <v>25</v>
       </c>
       <c r="D320" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E320" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F320" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="G320" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -10693,16 +10693,16 @@
         <v>50</v>
       </c>
       <c r="D321" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E321" t="n">
         <v>20</v>
       </c>
       <c r="F321" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G321" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -10725,16 +10725,16 @@
         <v>14</v>
       </c>
       <c r="D322" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E322" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F322" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G322" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -10757,16 +10757,16 @@
         <v>14</v>
       </c>
       <c r="D323" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E323" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F323" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G323" t="n">
-        <v>12</v>
+        <v>-1</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -10789,16 +10789,16 @@
         <v>14</v>
       </c>
       <c r="D324" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E324" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F324" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="G324" t="n">
-        <v>-16</v>
+        <v>4</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -10821,16 +10821,16 @@
         <v>14</v>
       </c>
       <c r="D325" t="n">
+        <v>11</v>
+      </c>
+      <c r="E325" t="n">
         <v>24</v>
       </c>
-      <c r="E325" t="n">
-        <v>13</v>
-      </c>
       <c r="F325" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G325" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -10949,16 +10949,16 @@
         <v>8</v>
       </c>
       <c r="D329" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E329" t="n">
         <v>0</v>
       </c>
       <c r="F329" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>-3</v>
+        <v>8</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -10981,16 +10981,16 @@
         <v>4</v>
       </c>
       <c r="D330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E330" t="n">
         <v>0</v>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -11045,16 +11045,16 @@
         <v>3</v>
       </c>
       <c r="D332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E332" t="n">
         <v>0</v>
       </c>
       <c r="F332" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H332" t="inlineStr">
         <is>
@@ -11141,16 +11141,16 @@
         <v>30</v>
       </c>
       <c r="D335" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E335" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F335" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="G335" t="n">
-        <v>18</v>
+        <v>-10</v>
       </c>
       <c r="H335" t="inlineStr">
         <is>
@@ -11173,16 +11173,16 @@
         <v>30</v>
       </c>
       <c r="D336" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E336" t="n">
         <v>0</v>
       </c>
       <c r="F336" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H336" t="inlineStr">
         <is>
@@ -11205,16 +11205,16 @@
         <v>30</v>
       </c>
       <c r="D337" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E337" t="n">
         <v>0</v>
       </c>
       <c r="F337" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G337" t="n">
-        <v>-15</v>
+        <v>15</v>
       </c>
       <c r="H337" t="inlineStr">
         <is>
@@ -11237,16 +11237,16 @@
         <v>30</v>
       </c>
       <c r="D338" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E338" t="n">
         <v>0</v>
       </c>
       <c r="F338" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G338" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H338" t="inlineStr">
         <is>
@@ -11269,16 +11269,16 @@
         <v>30</v>
       </c>
       <c r="D339" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E339" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F339" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="G339" t="n">
-        <v>19</v>
+        <v>-10</v>
       </c>
       <c r="H339" t="inlineStr">
         <is>
@@ -11365,16 +11365,16 @@
         <v>4</v>
       </c>
       <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>0</v>
+      </c>
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
         <v>4</v>
-      </c>
-      <c r="E342" t="n">
-        <v>0</v>
-      </c>
-      <c r="F342" t="n">
-        <v>4</v>
-      </c>
-      <c r="G342" t="n">
-        <v>0</v>
       </c>
       <c r="H342" t="inlineStr">
         <is>
@@ -11429,16 +11429,16 @@
         <v>14</v>
       </c>
       <c r="D344" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E344" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F344" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G344" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H344" t="inlineStr">
         <is>
@@ -11461,16 +11461,16 @@
         <v>14</v>
       </c>
       <c r="D345" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E345" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F345" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G345" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H345" t="inlineStr">
         <is>
@@ -11653,16 +11653,16 @@
         <v>36</v>
       </c>
       <c r="D351" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E351" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F351" t="n">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="G351" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H351" t="inlineStr">
         <is>
@@ -11685,16 +11685,16 @@
         <v>12</v>
       </c>
       <c r="D352" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E352" t="n">
         <v>0</v>
       </c>
       <c r="F352" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H352" t="inlineStr">
         <is>
@@ -11717,16 +11717,16 @@
         <v>18</v>
       </c>
       <c r="D353" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E353" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F353" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G353" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="H353" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Chocolate Kit Kat Blanco 41g</t>
+          <t>Chocolate Kit Kat Blanco 41,5g</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -11781,16 +11781,16 @@
         <v>24</v>
       </c>
       <c r="D355" t="n">
-        <v>-8</v>
+        <v>39</v>
       </c>
       <c r="E355" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F355" t="n">
-        <v>-8</v>
+        <v>87</v>
       </c>
       <c r="G355" t="n">
-        <v>32</v>
+        <v>-15</v>
       </c>
       <c r="H355" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Chocolate Kit Kat Milk 41g</t>
+          <t>Galleta Banada Choc Kit Kat Milk 41,5g</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11813,16 +11813,16 @@
         <v>24</v>
       </c>
       <c r="D356" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F356" t="n">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="G356" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="H356" t="inlineStr">
         <is>
@@ -11848,10 +11848,10 @@
         <v>7</v>
       </c>
       <c r="E357" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F357" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="G357" t="n">
         <v>6</v>
@@ -11877,16 +11877,16 @@
         <v>12</v>
       </c>
       <c r="D358" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E358" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F358" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="G358" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H358" t="inlineStr">
         <is>
@@ -11909,16 +11909,16 @@
         <v>12</v>
       </c>
       <c r="D359" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E359" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F359" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G359" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="H359" t="inlineStr">
         <is>
@@ -11941,16 +11941,16 @@
         <v>12</v>
       </c>
       <c r="D360" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F360" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G360" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H360" t="inlineStr">
         <is>
@@ -11973,16 +11973,16 @@
         <v>25</v>
       </c>
       <c r="D361" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E361" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F361" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G361" t="n">
-        <v>7</v>
+        <v>-4</v>
       </c>
       <c r="H361" t="inlineStr">
         <is>
@@ -12005,16 +12005,16 @@
         <v>30</v>
       </c>
       <c r="D362" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E362" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F362" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G362" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H362" t="inlineStr">
         <is>
@@ -12037,16 +12037,16 @@
         <v>28</v>
       </c>
       <c r="D363" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E363" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F363" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G363" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
@@ -12069,16 +12069,16 @@
         <v>20</v>
       </c>
       <c r="D364" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="E364" t="n">
         <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="G364" t="n">
-        <v>21</v>
+        <v>-3</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
@@ -12133,16 +12133,16 @@
         <v>20</v>
       </c>
       <c r="D366" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E366" t="n">
         <v>0</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G366" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
@@ -12165,16 +12165,16 @@
         <v>10</v>
       </c>
       <c r="D367" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E367" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F367" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G367" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
@@ -12229,16 +12229,16 @@
         <v>25</v>
       </c>
       <c r="D369" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="E369" t="n">
         <v>0</v>
       </c>
       <c r="F369" t="n">
-        <v>16</v>
+        <v>-1</v>
       </c>
       <c r="G369" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
@@ -12261,16 +12261,16 @@
         <v>7</v>
       </c>
       <c r="D370" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E370" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G370" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
@@ -12325,16 +12325,16 @@
         <v>7</v>
       </c>
       <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>15</v>
+      </c>
+      <c r="F372" t="n">
+        <v>15</v>
+      </c>
+      <c r="G372" t="n">
         <v>7</v>
-      </c>
-      <c r="E372" t="n">
-        <v>0</v>
-      </c>
-      <c r="F372" t="n">
-        <v>7</v>
-      </c>
-      <c r="G372" t="n">
-        <v>0</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
@@ -12357,16 +12357,16 @@
         <v>7</v>
       </c>
       <c r="D373" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E373" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F373" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G373" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="H373" t="inlineStr">
         <is>
@@ -12389,16 +12389,16 @@
         <v>20</v>
       </c>
       <c r="D374" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E374" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F374" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G374" t="n">
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
@@ -12421,16 +12421,16 @@
         <v>35</v>
       </c>
       <c r="D375" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E375" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="F375" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="G375" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -12453,16 +12453,16 @@
         <v>30</v>
       </c>
       <c r="D376" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E376" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F376" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G376" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H376" t="inlineStr">
         <is>
@@ -12517,16 +12517,16 @@
         <v>0</v>
       </c>
       <c r="D378" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E378" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -12549,16 +12549,16 @@
         <v>0</v>
       </c>
       <c r="D379" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E379" t="n">
         <v>0</v>
       </c>
       <c r="F379" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G379" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H379" t="inlineStr">
         <is>
@@ -12581,16 +12581,16 @@
         <v>25</v>
       </c>
       <c r="D380" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E380" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F380" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G380" t="n">
-        <v>-2</v>
+        <v>16</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
@@ -12613,16 +12613,16 @@
         <v>35</v>
       </c>
       <c r="D381" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="E381" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F381" t="n">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="G381" t="n">
-        <v>-4</v>
+        <v>19</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
@@ -12645,16 +12645,16 @@
         <v>32</v>
       </c>
       <c r="D382" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="E382" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F382" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G382" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="H382" t="inlineStr">
         <is>
@@ -12680,10 +12680,10 @@
         <v>0</v>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G383" t="n">
         <v>0</v>
@@ -12741,16 +12741,16 @@
         <v>12</v>
       </c>
       <c r="D385" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E385" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F385" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G385" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -12773,16 +12773,16 @@
         <v>15</v>
       </c>
       <c r="D386" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E386" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F386" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G386" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
@@ -12805,16 +12805,16 @@
         <v>20</v>
       </c>
       <c r="D387" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E387" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F387" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="G387" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H387" t="inlineStr">
         <is>
@@ -12837,16 +12837,16 @@
         <v>50</v>
       </c>
       <c r="D388" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E388" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F388" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="G388" t="n">
-        <v>-10</v>
+        <v>18</v>
       </c>
       <c r="H388" t="inlineStr">
         <is>
@@ -12869,16 +12869,16 @@
         <v>24</v>
       </c>
       <c r="D389" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E389" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="F389" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="G389" t="n">
-        <v>-12</v>
+        <v>20</v>
       </c>
       <c r="H389" t="inlineStr">
         <is>
@@ -12901,16 +12901,16 @@
         <v>15</v>
       </c>
       <c r="D390" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E390" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F390" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="G390" t="n">
-        <v>11</v>
+        <v>-8</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
@@ -12933,16 +12933,16 @@
         <v>20</v>
       </c>
       <c r="D391" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E391" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F391" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="G391" t="n">
-        <v>-13</v>
+        <v>7</v>
       </c>
       <c r="H391" t="inlineStr">
         <is>
@@ -12965,16 +12965,16 @@
         <v>20</v>
       </c>
       <c r="D392" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E392" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F392" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="G392" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
@@ -12997,16 +12997,16 @@
         <v>18</v>
       </c>
       <c r="D393" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E393" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F393" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="G393" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H393" t="inlineStr">
         <is>
@@ -13029,16 +13029,16 @@
         <v>20</v>
       </c>
       <c r="D394" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E394" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="F394" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G394" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
@@ -13064,10 +13064,10 @@
         <v>12</v>
       </c>
       <c r="E395" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F395" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G395" t="n">
         <v>0</v>
@@ -13125,16 +13125,16 @@
         <v>12</v>
       </c>
       <c r="D397" t="n">
-        <v>-6</v>
+        <v>14</v>
       </c>
       <c r="E397" t="n">
         <v>0</v>
       </c>
       <c r="F397" t="n">
-        <v>-6</v>
+        <v>14</v>
       </c>
       <c r="G397" t="n">
-        <v>18</v>
+        <v>-2</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
@@ -13157,16 +13157,16 @@
         <v>0</v>
       </c>
       <c r="D398" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E398" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F398" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="H398" t="inlineStr">
         <is>
@@ -13189,16 +13189,16 @@
         <v>12</v>
       </c>
       <c r="D399" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E399" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F399" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G399" t="n">
-        <v>6</v>
+        <v>-3</v>
       </c>
       <c r="H399" t="inlineStr">
         <is>
@@ -13221,16 +13221,16 @@
         <v>0</v>
       </c>
       <c r="D400" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E400" t="n">
         <v>0</v>
       </c>
       <c r="F400" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H400" t="inlineStr">
         <is>
@@ -13253,16 +13253,16 @@
         <v>24</v>
       </c>
       <c r="D401" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E401" t="n">
-        <v>20</v>
+        <v>571</v>
       </c>
       <c r="F401" t="n">
-        <v>31</v>
+        <v>576</v>
       </c>
       <c r="G401" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -13285,16 +13285,16 @@
         <v>24</v>
       </c>
       <c r="D402" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E402" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F402" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="G402" t="n">
-        <v>-9</v>
+        <v>-1</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
@@ -13317,16 +13317,16 @@
         <v>30</v>
       </c>
       <c r="D403" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E403" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F403" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G403" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
@@ -13349,16 +13349,16 @@
         <v>8</v>
       </c>
       <c r="D404" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E404" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F404" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G404" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="H404" t="inlineStr">
         <is>
@@ -13381,16 +13381,16 @@
         <v>20</v>
       </c>
       <c r="D405" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E405" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="F405" t="n">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="G405" t="n">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H405" t="inlineStr">
         <is>
@@ -13413,16 +13413,16 @@
         <v>21</v>
       </c>
       <c r="D406" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="E406" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F406" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G406" t="n">
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="H406" t="inlineStr">
         <is>
@@ -13445,16 +13445,16 @@
         <v>30</v>
       </c>
       <c r="D407" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E407" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F407" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="G407" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H407" t="inlineStr">
         <is>
@@ -13541,16 +13541,16 @@
         <v>14</v>
       </c>
       <c r="D410" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E410" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F410" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G410" t="n">
-        <v>-18</v>
+        <v>-16</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
@@ -13573,16 +13573,16 @@
         <v>30</v>
       </c>
       <c r="D411" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E411" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F411" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G411" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -13605,16 +13605,16 @@
         <v>24</v>
       </c>
       <c r="D412" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E412" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F412" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G412" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H412" t="inlineStr">
         <is>
@@ -13637,16 +13637,16 @@
         <v>24</v>
       </c>
       <c r="D413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E413" t="n">
         <v>0</v>
       </c>
       <c r="F413" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G413" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
@@ -13669,16 +13669,16 @@
         <v>24</v>
       </c>
       <c r="D414" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E414" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F414" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="G414" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="H414" t="inlineStr">
         <is>
@@ -13701,16 +13701,16 @@
         <v>20</v>
       </c>
       <c r="D415" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E415" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F415" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G415" t="n">
-        <v>-13</v>
+        <v>3</v>
       </c>
       <c r="H415" t="inlineStr">
         <is>
@@ -13733,16 +13733,16 @@
         <v>20</v>
       </c>
       <c r="D416" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E416" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F416" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G416" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H416" t="inlineStr">
         <is>
@@ -13765,16 +13765,16 @@
         <v>20</v>
       </c>
       <c r="D417" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="E417" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F417" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G417" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H417" t="inlineStr">
         <is>
@@ -13797,16 +13797,16 @@
         <v>20</v>
       </c>
       <c r="D418" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E418" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F418" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G418" t="n">
-        <v>-2</v>
+        <v>20</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
@@ -13861,16 +13861,16 @@
         <v>20</v>
       </c>
       <c r="D420" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E420" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F420" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G420" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H420" t="inlineStr">
         <is>
@@ -13893,16 +13893,16 @@
         <v>0</v>
       </c>
       <c r="D421" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E421" t="n">
         <v>0</v>
       </c>
       <c r="F421" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G421" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H421" t="inlineStr">
         <is>
@@ -13925,16 +13925,16 @@
         <v>36</v>
       </c>
       <c r="D422" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E422" t="n">
         <v>0</v>
       </c>
       <c r="F422" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G422" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H422" t="inlineStr">
         <is>
@@ -13989,16 +13989,16 @@
         <v>10</v>
       </c>
       <c r="D424" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E424" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F424" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G424" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="H424" t="inlineStr">
         <is>
@@ -14021,16 +14021,16 @@
         <v>10</v>
       </c>
       <c r="D425" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E425" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F425" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G425" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
@@ -14085,16 +14085,16 @@
         <v>70</v>
       </c>
       <c r="D427" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="E427" t="n">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="F427" t="n">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="G427" t="n">
-        <v>-8</v>
+        <v>22</v>
       </c>
       <c r="H427" t="inlineStr">
         <is>
@@ -14120,10 +14120,10 @@
         <v>8</v>
       </c>
       <c r="E428" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F428" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="G428" t="n">
         <v>2</v>
@@ -14181,16 +14181,16 @@
         <v>5</v>
       </c>
       <c r="D430" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E430" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F430" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G430" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H430" t="inlineStr">
         <is>
@@ -14216,10 +14216,10 @@
         <v>0</v>
       </c>
       <c r="E431" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F431" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G431" t="n">
         <v>5</v>
@@ -14245,16 +14245,16 @@
         <v>0</v>
       </c>
       <c r="D432" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E432" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F432" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G432" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H432" t="inlineStr">
         <is>
@@ -14277,16 +14277,16 @@
         <v>0</v>
       </c>
       <c r="D433" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E433" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F433" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G433" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr">
         <is>
@@ -14309,16 +14309,16 @@
         <v>8</v>
       </c>
       <c r="D434" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E434" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F434" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="G434" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H434" t="inlineStr">
         <is>
@@ -14341,16 +14341,16 @@
         <v>8</v>
       </c>
       <c r="D435" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E435" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F435" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G435" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="H435" t="inlineStr">
         <is>
@@ -14373,16 +14373,16 @@
         <v>8</v>
       </c>
       <c r="D436" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E436" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F436" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G436" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="H436" t="inlineStr">
         <is>
@@ -14533,16 +14533,16 @@
         <v>5</v>
       </c>
       <c r="D441" t="n">
+        <v>0</v>
+      </c>
+      <c r="E441" t="n">
+        <v>0</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0</v>
+      </c>
+      <c r="G441" t="n">
         <v>5</v>
-      </c>
-      <c r="E441" t="n">
-        <v>0</v>
-      </c>
-      <c r="F441" t="n">
-        <v>5</v>
-      </c>
-      <c r="G441" t="n">
-        <v>0</v>
       </c>
       <c r="H441" t="inlineStr">
         <is>
@@ -14597,16 +14597,16 @@
         <v>3</v>
       </c>
       <c r="D443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E443" t="n">
         <v>0</v>
       </c>
       <c r="F443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G443" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H443" t="inlineStr">
         <is>
@@ -14629,16 +14629,16 @@
         <v>4</v>
       </c>
       <c r="D444" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E444" t="n">
         <v>0</v>
       </c>
       <c r="F444" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G444" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H444" t="inlineStr">
         <is>
@@ -14661,16 +14661,16 @@
         <v>3</v>
       </c>
       <c r="D445" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E445" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F445" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G445" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="H445" t="inlineStr">
         <is>
@@ -14693,16 +14693,16 @@
         <v>30</v>
       </c>
       <c r="D446" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E446" t="n">
         <v>0</v>
       </c>
       <c r="F446" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G446" t="n">
-        <v>-2</v>
+        <v>17</v>
       </c>
       <c r="H446" t="inlineStr">
         <is>
@@ -14725,16 +14725,16 @@
         <v>25</v>
       </c>
       <c r="D447" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E447" t="n">
         <v>0</v>
       </c>
       <c r="F447" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G447" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H447" t="inlineStr">
         <is>
@@ -14757,16 +14757,16 @@
         <v>30</v>
       </c>
       <c r="D448" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E448" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F448" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="G448" t="n">
-        <v>-2</v>
+        <v>13</v>
       </c>
       <c r="H448" t="inlineStr">
         <is>
@@ -14789,16 +14789,16 @@
         <v>10</v>
       </c>
       <c r="D449" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E449" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F449" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="G449" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H449" t="inlineStr">
         <is>
@@ -14821,16 +14821,16 @@
         <v>12</v>
       </c>
       <c r="D450" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E450" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F450" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G450" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="H450" t="inlineStr">
         <is>
@@ -14853,16 +14853,16 @@
         <v>8</v>
       </c>
       <c r="D451" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E451" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F451" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G451" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
@@ -14888,10 +14888,10 @@
         <v>0</v>
       </c>
       <c r="E452" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F452" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G452" t="n">
         <v>4</v>
@@ -15016,10 +15016,10 @@
         <v>9</v>
       </c>
       <c r="E456" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F456" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G456" t="n">
         <v>-1</v>
@@ -15045,16 +15045,16 @@
         <v>40</v>
       </c>
       <c r="D457" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E457" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F457" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="G457" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H457" t="inlineStr">
         <is>
@@ -15077,16 +15077,16 @@
         <v>7</v>
       </c>
       <c r="D458" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E458" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F458" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G458" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="H458" t="inlineStr">
         <is>
@@ -15109,16 +15109,16 @@
         <v>10</v>
       </c>
       <c r="D459" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E459" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F459" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G459" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="H459" t="inlineStr">
         <is>
@@ -15141,16 +15141,16 @@
         <v>7</v>
       </c>
       <c r="D460" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E460" t="n">
         <v>0</v>
       </c>
       <c r="F460" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G460" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="H460" t="inlineStr">
         <is>
@@ -15173,16 +15173,16 @@
         <v>8</v>
       </c>
       <c r="D461" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E461" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F461" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G461" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="H461" t="inlineStr">
         <is>
@@ -15205,16 +15205,16 @@
         <v>7</v>
       </c>
       <c r="D462" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E462" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F462" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G462" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H462" t="inlineStr">
         <is>
@@ -15237,16 +15237,16 @@
         <v>7</v>
       </c>
       <c r="D463" t="n">
+        <v>15</v>
+      </c>
+      <c r="E463" t="n">
         <v>5</v>
       </c>
-      <c r="E463" t="n">
-        <v>10</v>
-      </c>
       <c r="F463" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G463" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="H463" t="inlineStr">
         <is>
@@ -15272,10 +15272,10 @@
         <v>4</v>
       </c>
       <c r="E464" t="n">
+        <v>0</v>
+      </c>
+      <c r="F464" t="n">
         <v>4</v>
-      </c>
-      <c r="F464" t="n">
-        <v>8</v>
       </c>
       <c r="G464" t="n">
         <v>0</v>
@@ -15333,16 +15333,16 @@
         <v>22</v>
       </c>
       <c r="D466" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E466" t="n">
         <v>0</v>
       </c>
       <c r="F466" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G466" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="H466" t="inlineStr">
         <is>
@@ -15365,16 +15365,16 @@
         <v>12</v>
       </c>
       <c r="D467" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E467" t="n">
         <v>0</v>
       </c>
       <c r="F467" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G467" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H467" t="inlineStr">
         <is>
@@ -15461,16 +15461,16 @@
         <v>20</v>
       </c>
       <c r="D470" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E470" t="n">
+        <v>46</v>
+      </c>
+      <c r="F470" t="n">
+        <v>53</v>
+      </c>
+      <c r="G470" t="n">
         <v>13</v>
-      </c>
-      <c r="F470" t="n">
-        <v>22</v>
-      </c>
-      <c r="G470" t="n">
-        <v>11</v>
       </c>
       <c r="H470" t="inlineStr">
         <is>
@@ -15525,16 +15525,16 @@
         <v>0</v>
       </c>
       <c r="D472" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E472" t="n">
         <v>0</v>
       </c>
       <c r="F472" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H472" t="inlineStr">
         <is>
